--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-11-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7ee22e8e5+80021]
+	GetHandleVerifier [0x0x7ff7ee22e940+80112]
+	(No symbol) [0x0x7ff7edfb060f]
+	(No symbol) [0x0x7ff7ee008854]
+	(No symbol) [0x0x7ff7ee008b1c]
+	(No symbol) [0x0x7ff7ee05c927]
+	(No symbol) [0x0x7ff7ee03126f]
+	(No symbol) [0x0x7ff7ee05968a]
+	(No symbol) [0x0x7ff7ee031003]
+	(No symbol) [0x0x7ff7edff95d1]
+	(No symbol) [0x0x7ff7edffa3f3]
+	GetHandleVerifier [0x0x7ff7ee4edc7d+2960429]
+	GetHandleVerifier [0x0x7ff7ee4e7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7ee508977+3070247]
+	GetHandleVerifier [0x0x7ff7ee2483ce+185214]
+	GetHandleVerifier [0x0x7ff7ee24fe1f+216527]
+	GetHandleVerifier [0x0x7ff7ee237b24+117460]
+	GetHandleVerifier [0x0x7ff7ee237cdf+117903]
+	GetHandleVerifier [0x0x7ff7ee21dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7e67ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7e67ae940+80112]
+	(No symbol) [0x0x7ff7e653060f]
+	(No symbol) [0x0x7ff7e6588854]
+	(No symbol) [0x0x7ff7e6588b1c]
+	(No symbol) [0x0x7ff7e65dc927]
+	(No symbol) [0x0x7ff7e65b126f]
+	(No symbol) [0x0x7ff7e65d968a]
+	(No symbol) [0x0x7ff7e65b1003]
+	(No symbol) [0x0x7ff7e65795d1]
+	(No symbol) [0x0x7ff7e657a3f3]
+	GetHandleVerifier [0x0x7ff7e6a6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7e6a67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7e6a88977+3070247]
+	GetHandleVerifier [0x0x7ff7e67c83ce+185214]
+	GetHandleVerifier [0x0x7ff7e67cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7e67b7b24+117460]
+	GetHandleVerifier [0x0x7ff7e67b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7e679dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>£28.38</t>
+          <t>£27.71</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7e67ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7e67ae940+80112]
+	(No symbol) [0x0x7ff7e653060f]
+	(No symbol) [0x0x7ff7e6588854]
+	(No symbol) [0x0x7ff7e6588b1c]
+	(No symbol) [0x0x7ff7e65dc927]
+	(No symbol) [0x0x7ff7e65b126f]
+	(No symbol) [0x0x7ff7e65d968a]
+	(No symbol) [0x0x7ff7e65b1003]
+	(No symbol) [0x0x7ff7e65795d1]
+	(No symbol) [0x0x7ff7e657a3f3]
+	GetHandleVerifier [0x0x7ff7e6a6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7e6a67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7e6a88977+3070247]
+	GetHandleVerifier [0x0x7ff7e67c83ce+185214]
+	GetHandleVerifier [0x0x7ff7e67cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7e67b7b24+117460]
+	GetHandleVerifier [0x0x7ff7e67b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7e679dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7e67ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7e67ae940+80112]
+	(No symbol) [0x0x7ff7e653060f]
+	(No symbol) [0x0x7ff7e6588854]
+	(No symbol) [0x0x7ff7e6588b1c]
+	(No symbol) [0x0x7ff7e65dc927]
+	(No symbol) [0x0x7ff7e65b126f]
+	(No symbol) [0x0x7ff7e65d968a]
+	(No symbol) [0x0x7ff7e65b1003]
+	(No symbol) [0x0x7ff7e65795d1]
+	(No symbol) [0x0x7ff7e657a3f3]
+	GetHandleVerifier [0x0x7ff7e6a6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7e6a67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7e6a88977+3070247]
+	GetHandleVerifier [0x0x7ff7e67c83ce+185214]
+	GetHandleVerifier [0x0x7ff7e67cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7e67b7b24+117460]
+	GetHandleVerifier [0x0x7ff7e67b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7e679dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7e67ae8e5+80021]
+	GetHandleVerifier [0x0x7ff7e67ae940+80112]
+	(No symbol) [0x0x7ff7e653060f]
+	(No symbol) [0x0x7ff7e6588854]
+	(No symbol) [0x0x7ff7e6588b1c]
+	(No symbol) [0x0x7ff7e65dc927]
+	(No symbol) [0x0x7ff7e65b126f]
+	(No symbol) [0x0x7ff7e65d968a]
+	(No symbol) [0x0x7ff7e65b1003]
+	(No symbol) [0x0x7ff7e65795d1]
+	(No symbol) [0x0x7ff7e657a3f3]
+	GetHandleVerifier [0x0x7ff7e6a6dc7d+2960429]
+	GetHandleVerifier [0x0x7ff7e6a67f3a+2936554]
+	GetHandleVerifier [0x0x7ff7e6a88977+3070247]
+	GetHandleVerifier [0x0x7ff7e67c83ce+185214]
+	GetHandleVerifier [0x0x7ff7e67cfe1f+216527]
+	GetHandleVerifier [0x0x7ff7e67b7b24+117460]
+	GetHandleVerifier [0x0x7ff7e67b7cdf+117903]
+	GetHandleVerifier [0x0x7ff7e679dbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff65b5fe8e5+80021]
+	GetHandleVerifier [0x0x7ff65b5fe940+80112]
+	(No symbol) [0x0x7ff65b38060f]
+	(No symbol) [0x0x7ff65b3d8854]
+	(No symbol) [0x0x7ff65b3d8b1c]
+	(No symbol) [0x0x7ff65b42c927]
+	(No symbol) [0x0x7ff65b40126f]
+	(No symbol) [0x0x7ff65b42968a]
+	(No symbol) [0x0x7ff65b401003]
+	(No symbol) [0x0x7ff65b3c95d1]
+	(No symbol) [0x0x7ff65b3ca3f3]
+	GetHandleVerifier [0x0x7ff65b8bdc7d+2960429]
+	GetHandleVerifier [0x0x7ff65b8b7f3a+2936554]
+	GetHandleVerifier [0x0x7ff65b8d8977+3070247]
+	GetHandleVerifier [0x0x7ff65b6183ce+185214]
+	GetHandleVerifier [0x0x7ff65b61fe1f+216527]
+	GetHandleVerifier [0x0x7ff65b607b24+117460]
+	GetHandleVerifier [0x0x7ff65b607cdf+117903]
+	GetHandleVerifier [0x0x7ff65b5edbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7444fe8e5+80021]
+	GetHandleVerifier [0x0x7ff7444fe940+80112]
+	(No symbol) [0x0x7ff74428060f]
+	(No symbol) [0x0x7ff7442d8854]
+	(No symbol) [0x0x7ff7442d8b1c]
+	(No symbol) [0x0x7ff74432c927]
+	(No symbol) [0x0x7ff74430126f]
+	(No symbol) [0x0x7ff74432968a]
+	(No symbol) [0x0x7ff744301003]
+	(No symbol) [0x0x7ff7442c95d1]
+	(No symbol) [0x0x7ff7442ca3f3]
+	GetHandleVerifier [0x0x7ff7447bdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7447b7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7447d8977+3070247]
+	GetHandleVerifier [0x0x7ff7445183ce+185214]
+	GetHandleVerifier [0x0x7ff74451fe1f+216527]
+	GetHandleVerifier [0x0x7ff744507b24+117460]
+	GetHandleVerifier [0x0x7ff744507cdf+117903]
+	GetHandleVerifier [0x0x7ff7444edbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7444fe8e5+80021]
+	GetHandleVerifier [0x0x7ff7444fe940+80112]
+	(No symbol) [0x0x7ff74428060f]
+	(No symbol) [0x0x7ff7442d8854]
+	(No symbol) [0x0x7ff7442d8b1c]
+	(No symbol) [0x0x7ff74432c927]
+	(No symbol) [0x0x7ff74430126f]
+	(No symbol) [0x0x7ff74432968a]
+	(No symbol) [0x0x7ff744301003]
+	(No symbol) [0x0x7ff7442c95d1]
+	(No symbol) [0x0x7ff7442ca3f3]
+	GetHandleVerifier [0x0x7ff7447bdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7447b7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7447d8977+3070247]
+	GetHandleVerifier [0x0x7ff7445183ce+185214]
+	GetHandleVerifier [0x0x7ff74451fe1f+216527]
+	GetHandleVerifier [0x0x7ff744507b24+117460]
+	GetHandleVerifier [0x0x7ff744507cdf+117903]
+	GetHandleVerifier [0x0x7ff7444edbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7444fe8e5+80021]
+	GetHandleVerifier [0x0x7ff7444fe940+80112]
+	(No symbol) [0x0x7ff74428060f]
+	(No symbol) [0x0x7ff7442d8854]
+	(No symbol) [0x0x7ff7442d8b1c]
+	(No symbol) [0x0x7ff74432c927]
+	(No symbol) [0x0x7ff74430126f]
+	(No symbol) [0x0x7ff74432968a]
+	(No symbol) [0x0x7ff744301003]
+	(No symbol) [0x0x7ff7442c95d1]
+	(No symbol) [0x0x7ff7442ca3f3]
+	GetHandleVerifier [0x0x7ff7447bdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7447b7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7447d8977+3070247]
+	GetHandleVerifier [0x0x7ff7445183ce+185214]
+	GetHandleVerifier [0x0x7ff74451fe1f+216527]
+	GetHandleVerifier [0x0x7ff744507b24+117460]
+	GetHandleVerifier [0x0x7ff744507cdf+117903]
+	GetHandleVerifier [0x0x7ff7444edbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.123); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff655e2e8e5+80021]
-	GetHandleVerifier [0x0x7ff655e2e940+80112]
-	(No symbol) [0x0x7ff655bb060f]
-	(No symbol) [0x0x7ff655c08854]
-	(No symbol) [0x0x7ff655c08b1c]
-	(No symbol) [0x0x7ff655c5c927]
-	(No symbol) [0x0x7ff655c3126f]
-	(No symbol) [0x0x7ff655c5968a]
-	(No symbol) [0x0x7ff655c31003]
-	(No symbol) [0x0x7ff655bf95d1]
-	(No symbol) [0x0x7ff655bfa3f3]
-	GetHandleVerifier [0x0x7ff6560edc7d+2960429]
-	GetHandleVerifier [0x0x7ff6560e7f3a+2936554]
-	GetHandleVerifier [0x0x7ff656108977+3070247]
-	GetHandleVerifier [0x0x7ff655e483ce+185214]
-	GetHandleVerifier [0x0x7ff655e4fe1f+216527]
-	GetHandleVerifier [0x0x7ff655e37b24+117460]
-	GetHandleVerifier [0x0x7ff655e37cdf+117903]
-	GetHandleVerifier [0x0x7ff655e1dbb8+11112]
+	GetHandleVerifier [0x0x7ff7444fe8e5+80021]
+	GetHandleVerifier [0x0x7ff7444fe940+80112]
+	(No symbol) [0x0x7ff74428060f]
+	(No symbol) [0x0x7ff7442d8854]
+	(No symbol) [0x0x7ff7442d8b1c]
+	(No symbol) [0x0x7ff74432c927]
+	(No symbol) [0x0x7ff74430126f]
+	(No symbol) [0x0x7ff74432968a]
+	(No symbol) [0x0x7ff744301003]
+	(No symbol) [0x0x7ff7442c95d1]
+	(No symbol) [0x0x7ff7442ca3f3]
+	GetHandleVerifier [0x0x7ff7447bdc7d+2960429]
+	GetHandleVerifier [0x0x7ff7447b7f3a+2936554]
+	GetHandleVerifier [0x0x7ff7447d8977+3070247]
+	GetHandleVerifier [0x0x7ff7445183ce+185214]
+	GetHandleVerifier [0x0x7ff74451fe1f+216527]
+	GetHandleVerifier [0x0x7ff744507b24+117460]
+	GetHandleVerifier [0x0x7ff744507cdf+117903]
+	GetHandleVerifier [0x0x7ff7444edbb8+11112]
 	BaseThreadInitThunk [0x0x7ff8c8a7e8d7+23]
 	RtlUserThreadStart [0x0x7ff8c9fac53c+44]
 </t>
